--- a/Proyecto Interno/Revisión de literatura/Revision literatura (sistemas agroalimentarios)/matriz_sistemas.xlsx
+++ b/Proyecto Interno/Revisión de literatura/Revision literatura (sistemas agroalimentarios)/matriz_sistemas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/Revisión de literatura/Revision literatura (sistemas agroalimentarios)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB57A7BC-D7F0-42B5-A5EA-5B711874EEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{CB57A7BC-D7F0-42B5-A5EA-5B711874EEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A57881EF-421E-4465-A7CD-1D0DEF8AAA9A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58EE180D-9C68-4B84-A498-E1A9239C831F}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" xr2:uid="{58EE180D-9C68-4B84-A498-E1A9239C831F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Documento</t>
   </si>
@@ -325,6 +325,91 @@
   </si>
   <si>
     <t>Reina, et al (A).</t>
+  </si>
+  <si>
+    <t>Building a more sustainable food system in Colombia</t>
+  </si>
+  <si>
+    <t>Paper académico</t>
+  </si>
+  <si>
+    <t>Analiza la transición hacia sistemas alimentarios sostenibles en Colombia, incluyendo seguridad alimentaria, desigualdad, agroecología y sostenibilidad. Destaca que la inseguridad alimentaria está ligada a pobreza, desigualdad y acceso económico a alimentos.</t>
+  </si>
+  <si>
+    <t>Rankin &amp; Bonilla-Findji – CGIAR / CIAT / WLE</t>
+  </si>
+  <si>
+    <t>Report técnico</t>
+  </si>
+  <si>
+    <t>Analiza sistemas alimentarios urbanos en América Latina desde enfoque city-region food systems (CRFS), incluyendo gobernanza, sostenibilidad, seguridad alimentaria y resiliencia.</t>
+  </si>
+  <si>
+    <t>What can the Latin American cities of Cali, Quito and Medellín learn from each other’s efforts</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Bogotá</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: evidencia de agricultura urbana como estrategia para mejorar acceso a alimentos y seguridad alimentaria. En general, las ciudades enfrentan problemas de affordability y acceso económico a dietas saludables.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cali</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: enfoque en seguridad alimentaria y nutricional (malnutrición + obesidad). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Medellín</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: énfasis en cadenas cortas de abastecimiento y brecha urbano-rural. Ambos casos muestran problemas de acceso y desigualdad en alimentos.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gómez, et al</t>
   </si>
 </sst>
 </file>
@@ -395,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -404,6 +489,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -421,6 +509,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -740,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD0CF362-44FA-4098-989E-7E183A343E0C}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.5546875" customWidth="1"/>
@@ -929,6 +1021,86 @@
         <v>36</v>
       </c>
     </row>
+    <row r="10" spans="1:6" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
